--- a/project/output/nasa-tlx/analysis_results/statistical_results.xlsx
+++ b/project/output/nasa-tlx/analysis_results/statistical_results.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-01-21 13:37:55</t>
+          <t>2026-02-03 23:47:44</t>
         </is>
       </c>
     </row>

--- a/project/output/nasa-tlx/analysis_results/statistical_results.xlsx
+++ b/project/output/nasa-tlx/analysis_results/statistical_results.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-03 23:47:44</t>
+          <t>2026-02-04 09:52:53</t>
         </is>
       </c>
     </row>

--- a/project/output/nasa-tlx/analysis_results/statistical_results.xlsx
+++ b/project/output/nasa-tlx/analysis_results/statistical_results.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-04 09:52:53</t>
+          <t>2026-02-09 19:01:34</t>
         </is>
       </c>
     </row>
